--- a/tiflow-rx/build/1.0.0-draft/StructureDefinition-GEM-ERP-PR-AuditEvent.xlsx
+++ b/tiflow-rx/build/1.0.0-draft/StructureDefinition-GEM-ERP-PR-AuditEvent.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3183" uniqueCount="570">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3167" uniqueCount="563">
   <si>
     <t>Property</t>
   </si>
@@ -457,6 +457,94 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>AuditEvent.modifierExtension</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+  </si>
+  <si>
+    <t>DomainResource.modifierExtension</t>
+  </si>
+  <si>
+    <t>AuditEvent.type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Type/identifier of event</t>
+  </si>
+  <si>
+    <t>Identifier for a family of the event.  For example, a menu item, program, rule, policy, function code, application name or URL. It identifies the performed function.</t>
+  </si>
+  <si>
+    <t>This identifies the performed function. For "Execute" Event Action Code audit records, this identifies the application function performed.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Type of event.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/audit-event-type|4.0.1</t>
+  </si>
+  <si>
+    <t>Event.code</t>
+  </si>
+  <si>
+    <t>.code (type, subtype and action are pre-coordinated or sent as translations)</t>
+  </si>
+  <si>
+    <t>EventId</t>
+  </si>
+  <si>
+    <t>FiveWs.what[x]</t>
+  </si>
+  <si>
+    <t>Activity</t>
+  </si>
+  <si>
+    <t>AuditEvent.type.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>AuditEvent.type.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
     <t xml:space="preserve">value:url}
 </t>
   </si>
@@ -467,101 +555,6 @@
     <t>open</t>
   </si>
   <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>AuditEvent.modifierExtension</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
-  </si>
-  <si>
-    <t>DomainResource.modifierExtension</t>
-  </si>
-  <si>
-    <t>AuditEvent.type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Type/identifier of event</t>
-  </si>
-  <si>
-    <t>Identifier for a family of the event.  For example, a menu item, program, rule, policy, function code, application name or URL. It identifies the performed function.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.</t>
-  </si>
-  <si>
-    <t>This identifies the performed function. For "Execute" Event Action Code audit records, this identifies the application function performed.</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>Type of event.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/audit-event-type|4.0.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>Event.code</t>
-  </si>
-  <si>
-    <t>.code (type, subtype and action are pre-coordinated or sent as translations)</t>
-  </si>
-  <si>
-    <t>EventId</t>
-  </si>
-  <si>
-    <t>FiveWs.what[x]</t>
-  </si>
-  <si>
-    <t>Activity</t>
-  </si>
-  <si>
-    <t>AuditEvent.type.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>AuditEvent.type.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
     <t>Element.extension</t>
   </si>
   <si>
@@ -635,9 +628,6 @@
   </si>
   <si>
     <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
   </si>
   <si>
     <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
@@ -735,10 +725,6 @@
     <t>The period can be a little arbitrary; where possible, the time should correspond to human assessment of the activity time.</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
-  </si>
-  <si>
     <t>Event.occurred[x]</t>
   </si>
   <si>
@@ -939,9 +925,6 @@
     <t>Specification of the participation type the user plays when performing the event.</t>
   </si>
   <si>
-    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
-  </si>
-  <si>
     <t>The Participation type of the agent to the event.</t>
   </si>
   <si>
@@ -1014,10 +997,6 @@
   </si>
   <si>
     <t>This field ties an audit event to a specific resource or identifier.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -1192,9 +1171,6 @@
     <t>Where the event occurred.</t>
   </si>
   <si>
-    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
-  </si>
-  <si>
     <t>Event.location</t>
   </si>
   <si>
@@ -1392,7 +1368,7 @@
     <t>This value differentiates among the sites in a multi-site enterprise health information system.</t>
   </si>
   <si>
-    <t>E-Rezept Fachdienst</t>
+    <t>E-Rezept-Fachdienst</t>
   </si>
   <si>
     <t>.scopedRole[classCode=LOCE].player.desc</t>
@@ -3187,19 +3163,19 @@
         <v>80</v>
       </c>
       <c r="AB9" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD9" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE9" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF9" t="s" s="2">
         <v>142</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="AD9" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE9" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="AF9" t="s" s="2">
-        <v>145</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>81</v>
@@ -3211,7 +3187,7 @@
         <v>80</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>80</v>
@@ -3234,10 +3210,10 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -3263,16 +3239,16 @@
         <v>138</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="N10" t="s" s="2">
         <v>141</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>80</v>
@@ -3309,19 +3285,19 @@
         <v>80</v>
       </c>
       <c r="AB10" t="s" s="2">
-        <v>142</v>
+        <v>80</v>
       </c>
       <c r="AC10" t="s" s="2">
-        <v>143</v>
+        <v>80</v>
       </c>
       <c r="AD10" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>144</v>
+        <v>80</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>81</v>
@@ -3333,7 +3309,7 @@
         <v>80</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>80</v>
@@ -3356,10 +3332,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3382,19 +3358,17 @@
         <v>93</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L11" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="M11" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="N11" s="2"/>
+      <c r="O11" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="L11" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="O11" t="s" s="2">
-        <v>157</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>80</v>
@@ -3419,13 +3393,13 @@
         <v>80</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>80</v>
@@ -3443,7 +3417,7 @@
         <v>80</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>92</v>
@@ -3452,25 +3426,25 @@
         <v>92</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>161</v>
+        <v>80</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="AP11" t="s" s="2">
         <v>80</v>
@@ -3478,10 +3452,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3504,13 +3478,13 @@
         <v>80</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -3561,7 +3535,7 @@
         <v>80</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>81</v>
@@ -3579,7 +3553,7 @@
         <v>80</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>80</v>
@@ -3596,10 +3570,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3628,7 +3602,7 @@
         <v>139</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="N13" t="s" s="2">
         <v>141</v>
@@ -3669,19 +3643,19 @@
         <v>80</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>142</v>
+        <v>170</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>143</v>
+        <v>171</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>144</v>
+        <v>172</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>81</v>
@@ -3693,13 +3667,13 @@
         <v>80</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>80</v>
@@ -3716,10 +3690,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3745,23 +3719,23 @@
         <v>106</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="N14" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="O14" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="S14" t="s" s="2">
         <v>80</v>
@@ -3803,7 +3777,7 @@
         <v>80</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>81</v>
@@ -3821,7 +3795,7 @@
         <v>80</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>80</v>
@@ -3838,10 +3812,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3864,16 +3838,16 @@
         <v>93</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="N15" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3923,7 +3897,7 @@
         <v>80</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>81</v>
@@ -3941,7 +3915,7 @@
         <v>80</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>80</v>
@@ -3958,10 +3932,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3987,21 +3961,21 @@
         <v>112</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="S16" t="s" s="2">
         <v>80</v>
@@ -4043,7 +4017,7 @@
         <v>80</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>81</v>
@@ -4061,7 +4035,7 @@
         <v>80</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>80</v>
@@ -4078,10 +4052,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4104,19 +4078,17 @@
         <v>93</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="M17" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="N17" s="2"/>
+      <c r="O17" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>201</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>80</v>
@@ -4165,7 +4137,7 @@
         <v>80</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -4183,7 +4155,7 @@
         <v>80</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>80</v>
@@ -4200,10 +4172,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4226,19 +4198,19 @@
         <v>93</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="N18" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>209</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>80</v>
@@ -4287,7 +4259,7 @@
         <v>80</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4305,7 +4277,7 @@
         <v>80</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>80</v>
@@ -4322,10 +4294,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4348,19 +4320,17 @@
         <v>93</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>156</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" t="s" s="2">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>80</v>
@@ -4385,13 +4355,13 @@
         <v>80</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>80</v>
@@ -4409,7 +4379,7 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4418,7 +4388,7 @@
         <v>82</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>161</v>
+        <v>80</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>104</v>
@@ -4427,13 +4397,13 @@
         <v>80</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>80</v>
@@ -4444,10 +4414,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4473,14 +4443,14 @@
         <v>112</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" t="s" s="2">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>80</v>
@@ -4505,13 +4475,13 @@
         <v>80</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>80</v>
@@ -4529,7 +4499,7 @@
         <v>80</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4547,13 +4517,13 @@
         <v>80</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>80</v>
@@ -4564,10 +4534,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4590,16 +4560,16 @@
         <v>80</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="N21" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="L21" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>231</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4649,7 +4619,7 @@
         <v>80</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4658,36 +4628,36 @@
         <v>92</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>161</v>
+        <v>80</v>
       </c>
       <c r="AJ21" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK21" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AM21" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AN21" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="AK21" t="s" s="2">
+      <c r="AO21" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="AL21" t="s" s="2">
+      <c r="AP21" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="AP21" t="s" s="2">
-        <v>238</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4710,19 +4680,19 @@
         <v>93</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="M22" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="O22" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="L22" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>244</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>80</v>
@@ -4771,7 +4741,7 @@
         <v>80</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>92</v>
@@ -4789,27 +4759,27 @@
         <v>80</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4835,13 +4805,13 @@
         <v>112</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4867,13 +4837,13 @@
         <v>80</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>80</v>
@@ -4891,7 +4861,7 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4909,13 +4879,13 @@
         <v>80</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>80</v>
@@ -4926,10 +4896,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4952,17 +4922,15 @@
         <v>93</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>200</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>80</v>
@@ -5011,7 +4979,7 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -5029,13 +4997,13 @@
         <v>80</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>80</v>
@@ -5046,10 +5014,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5072,16 +5040,16 @@
         <v>93</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5107,13 +5075,13 @@
         <v>80</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>80</v>
@@ -5131,7 +5099,7 @@
         <v>80</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -5140,40 +5108,40 @@
         <v>82</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>161</v>
+        <v>80</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="AN25" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="AO25" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="AL25" t="s" s="2">
+      <c r="AP25" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="AP25" t="s" s="2">
-        <v>273</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -5192,19 +5160,19 @@
         <v>80</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="O26" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="L26" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>80</v>
@@ -5253,7 +5221,7 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>92</v>
@@ -5262,36 +5230,36 @@
         <v>82</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>161</v>
+        <v>80</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AN26" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AO26" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="AL26" t="s" s="2">
+      <c r="AP26" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="AP26" t="s" s="2">
-        <v>286</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5314,13 +5282,13 @@
         <v>80</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5371,7 +5339,7 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5389,7 +5357,7 @@
         <v>80</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>80</v>
@@ -5406,10 +5374,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5438,7 +5406,7 @@
         <v>139</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="N28" t="s" s="2">
         <v>141</v>
@@ -5479,19 +5447,19 @@
         <v>80</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>142</v>
+        <v>80</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>143</v>
+        <v>80</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>144</v>
+        <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5503,13 +5471,13 @@
         <v>80</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>80</v>
@@ -5526,14 +5494,14 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5555,16 +5523,16 @@
         <v>138</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="N29" t="s" s="2">
         <v>141</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>80</v>
@@ -5613,7 +5581,7 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5625,7 +5593,7 @@
         <v>80</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>80</v>
@@ -5648,10 +5616,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5674,17 +5642,15 @@
         <v>80</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>297</v>
-      </c>
+        <v>292</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>80</v>
@@ -5709,13 +5675,13 @@
         <v>80</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>80</v>
@@ -5733,7 +5699,7 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5742,36 +5708,36 @@
         <v>92</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>161</v>
+        <v>80</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>304</v>
+        <v>299</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5794,19 +5760,19 @@
         <v>80</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>80</v>
@@ -5831,13 +5797,13 @@
         <v>80</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>80</v>
@@ -5855,7 +5821,7 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5864,7 +5830,7 @@
         <v>82</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>161</v>
+        <v>80</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>104</v>
@@ -5873,31 +5839,31 @@
         <v>80</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>314</v>
+        <v>309</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5916,19 +5882,19 @@
         <v>93</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>80</v>
@@ -5977,7 +5943,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5986,36 +5952,36 @@
         <v>92</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>161</v>
+        <v>80</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>322</v>
+        <v>104</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>327</v>
+        <v>321</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6038,13 +6004,13 @@
         <v>80</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6095,7 +6061,7 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -6113,7 +6079,7 @@
         <v>80</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>80</v>
@@ -6130,10 +6096,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6162,7 +6128,7 @@
         <v>139</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>141</v>
@@ -6203,19 +6169,19 @@
         <v>80</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>142</v>
+        <v>170</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>143</v>
+        <v>171</v>
       </c>
       <c r="AD34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>144</v>
+        <v>172</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6227,13 +6193,13 @@
         <v>80</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>80</v>
@@ -6250,10 +6216,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6276,16 +6242,16 @@
         <v>93</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6335,7 +6301,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6344,7 +6310,7 @@
         <v>92</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>104</v>
@@ -6370,10 +6336,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6399,13 +6365,13 @@
         <v>106</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6431,13 +6397,13 @@
         <v>80</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>80</v>
@@ -6455,7 +6421,7 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6490,10 +6456,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6516,16 +6482,16 @@
         <v>93</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6575,7 +6541,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6584,7 +6550,7 @@
         <v>92</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>161</v>
+        <v>80</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>104</v>
@@ -6593,7 +6559,7 @@
         <v>80</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>80</v>
@@ -6610,10 +6576,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6636,16 +6602,16 @@
         <v>93</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6695,7 +6661,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6730,10 +6696,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6756,19 +6722,17 @@
         <v>80</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>200</v>
-      </c>
+        <v>351</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>80</v>
@@ -6817,7 +6781,7 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6835,16 +6799,16 @@
         <v>80</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>80</v>
@@ -6852,10 +6816,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6878,19 +6842,17 @@
         <v>80</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>200</v>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>80</v>
@@ -6939,7 +6901,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -6957,16 +6919,16 @@
         <v>80</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>80</v>
@@ -6974,10 +6936,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7000,19 +6962,19 @@
         <v>93</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>80</v>
@@ -7061,7 +7023,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>92</v>
@@ -7079,13 +7041,13 @@
         <v>80</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>80</v>
@@ -7096,10 +7058,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7122,17 +7084,15 @@
         <v>80</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>378</v>
-      </c>
+        <v>371</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>80</v>
@@ -7181,45 +7141,45 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK42" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN42" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="AG42" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH42" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI42" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="AJ42" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="AK42" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="AL42" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>381</v>
-      </c>
       <c r="AO42" t="s" s="2">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>383</v>
+        <v>376</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7245,16 +7205,16 @@
         <v>106</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>80</v>
@@ -7303,7 +7263,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7321,27 +7281,27 @@
         <v>80</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>391</v>
+        <v>384</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7364,19 +7324,17 @@
         <v>80</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>156</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>80</v>
@@ -7401,13 +7359,13 @@
         <v>80</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>80</v>
@@ -7425,7 +7383,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7434,7 +7392,7 @@
         <v>92</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>161</v>
+        <v>80</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>104</v>
@@ -7443,13 +7401,13 @@
         <v>80</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>80</v>
@@ -7460,10 +7418,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7486,13 +7444,13 @@
         <v>80</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7543,7 +7501,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7552,7 +7510,7 @@
         <v>92</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>161</v>
+        <v>80</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>104</v>
@@ -7561,13 +7519,13 @@
         <v>80</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>80</v>
@@ -7578,10 +7536,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7604,13 +7562,13 @@
         <v>80</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7661,7 +7619,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7679,7 +7637,7 @@
         <v>80</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>80</v>
@@ -7696,10 +7654,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7728,7 +7686,7 @@
         <v>139</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>141</v>
@@ -7769,19 +7727,19 @@
         <v>80</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>142</v>
+        <v>80</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>143</v>
+        <v>80</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>144</v>
+        <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7793,13 +7751,13 @@
         <v>80</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>80</v>
@@ -7816,14 +7774,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7845,16 +7803,16 @@
         <v>138</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="N48" t="s" s="2">
         <v>141</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>80</v>
@@ -7903,7 +7861,7 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7915,7 +7873,7 @@
         <v>80</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>80</v>
@@ -7938,10 +7896,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7964,19 +7922,19 @@
         <v>80</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>80</v>
@@ -8025,7 +7983,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8043,16 +8001,16 @@
         <v>80</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>80</v>
@@ -8060,10 +8018,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8089,14 +8047,14 @@
         <v>112</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>80</v>
@@ -8121,13 +8079,13 @@
         <v>80</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>80</v>
@@ -8145,7 +8103,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8163,13 +8121,13 @@
         <v>80</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>80</v>
@@ -8180,10 +8138,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8206,16 +8164,16 @@
         <v>80</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8241,13 +8199,13 @@
         <v>80</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>80</v>
@@ -8265,7 +8223,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8274,7 +8232,7 @@
         <v>82</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>161</v>
+        <v>80</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>104</v>
@@ -8283,16 +8241,16 @@
         <v>80</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>80</v>
@@ -8300,10 +8258,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8326,19 +8284,19 @@
         <v>80</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>80</v>
@@ -8387,7 +8345,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>92</v>
@@ -8396,7 +8354,7 @@
         <v>92</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>161</v>
+        <v>80</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>104</v>
@@ -8405,13 +8363,13 @@
         <v>80</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>80</v>
@@ -8422,10 +8380,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8448,13 +8406,13 @@
         <v>80</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8505,7 +8463,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8523,7 +8481,7 @@
         <v>80</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>80</v>
@@ -8540,10 +8498,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8572,7 +8530,7 @@
         <v>139</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>141</v>
@@ -8613,19 +8571,19 @@
         <v>80</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>142</v>
+        <v>80</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>143</v>
+        <v>80</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>144</v>
+        <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8637,13 +8595,13 @@
         <v>80</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>80</v>
@@ -8660,14 +8618,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8689,16 +8647,16 @@
         <v>138</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>141</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>80</v>
@@ -8747,7 +8705,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8759,7 +8717,7 @@
         <v>80</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>80</v>
@@ -8782,10 +8740,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8808,26 +8766,24 @@
         <v>80</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>200</v>
-      </c>
+        <v>434</v>
+      </c>
+      <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>442</v>
+        <v>435</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q56" s="2"/>
       <c r="R56" t="s" s="2">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="S56" t="s" s="2">
         <v>80</v>
@@ -8869,7 +8825,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8887,13 +8843,13 @@
         <v>80</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>80</v>
@@ -8904,14 +8860,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8930,19 +8886,17 @@
         <v>93</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>378</v>
-      </c>
+        <v>443</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>80</v>
@@ -8991,7 +8945,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>92</v>
@@ -9000,22 +8954,22 @@
         <v>92</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>161</v>
+        <v>80</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>322</v>
+        <v>104</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>80</v>
@@ -9026,10 +8980,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9052,13 +9006,13 @@
         <v>80</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9109,7 +9063,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9127,7 +9081,7 @@
         <v>80</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>80</v>
@@ -9144,10 +9098,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9176,7 +9130,7 @@
         <v>139</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="N59" t="s" s="2">
         <v>141</v>
@@ -9217,19 +9171,19 @@
         <v>80</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>142</v>
+        <v>170</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>143</v>
+        <v>171</v>
       </c>
       <c r="AD59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>144</v>
+        <v>172</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9241,13 +9195,13 @@
         <v>80</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>80</v>
@@ -9264,10 +9218,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9290,16 +9244,16 @@
         <v>93</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9349,7 +9303,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9358,7 +9312,7 @@
         <v>92</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>104</v>
@@ -9384,10 +9338,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9413,13 +9367,13 @@
         <v>106</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9445,13 +9399,13 @@
         <v>80</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>80</v>
@@ -9469,7 +9423,7 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9504,10 +9458,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>457</v>
+        <v>450</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>457</v>
+        <v>450</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9530,16 +9484,16 @@
         <v>93</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9589,7 +9543,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9598,7 +9552,7 @@
         <v>92</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>161</v>
+        <v>80</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>104</v>
@@ -9607,7 +9561,7 @@
         <v>80</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>80</v>
@@ -9624,10 +9578,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9650,16 +9604,16 @@
         <v>93</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9709,7 +9663,7 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9744,10 +9698,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9770,19 +9724,17 @@
         <v>80</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>156</v>
-      </c>
+        <v>455</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>80</v>
@@ -9807,13 +9759,13 @@
         <v>80</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>80</v>
@@ -9831,7 +9783,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9840,7 +9792,7 @@
         <v>82</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>161</v>
+        <v>80</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>104</v>
@@ -9849,13 +9801,13 @@
         <v>80</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>80</v>
@@ -9866,14 +9818,14 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9892,19 +9844,19 @@
         <v>80</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>80</v>
@@ -9953,7 +9905,7 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -9962,36 +9914,36 @@
         <v>82</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>161</v>
+        <v>80</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>478</v>
+        <v>471</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10014,13 +9966,13 @@
         <v>80</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10071,7 +10023,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10089,7 +10041,7 @@
         <v>80</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>80</v>
@@ -10106,10 +10058,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10138,7 +10090,7 @@
         <v>139</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>141</v>
@@ -10179,19 +10131,19 @@
         <v>80</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>142</v>
+        <v>80</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>143</v>
+        <v>80</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>144</v>
+        <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10203,13 +10155,13 @@
         <v>80</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>80</v>
@@ -10226,14 +10178,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10255,16 +10207,16 @@
         <v>138</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="N68" t="s" s="2">
         <v>141</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>80</v>
@@ -10313,7 +10265,7 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10325,7 +10277,7 @@
         <v>80</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>80</v>
@@ -10348,10 +10300,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10374,17 +10326,15 @@
         <v>93</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>483</v>
+        <v>476</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>378</v>
-      </c>
+        <v>478</v>
+      </c>
+      <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>80</v>
@@ -10433,7 +10383,7 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10442,36 +10392,36 @@
         <v>92</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>161</v>
+        <v>80</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>322</v>
+        <v>104</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>487</v>
+        <v>480</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10494,19 +10444,19 @@
         <v>80</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>491</v>
+        <v>484</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>80</v>
@@ -10531,13 +10481,13 @@
         <v>80</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>80</v>
@@ -10555,7 +10505,7 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10564,7 +10514,7 @@
         <v>92</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>161</v>
+        <v>80</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>104</v>
@@ -10573,27 +10523,27 @@
         <v>80</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>498</v>
+        <v>491</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10616,19 +10566,17 @@
         <v>80</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>156</v>
-      </c>
+        <v>494</v>
+      </c>
+      <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>80</v>
@@ -10653,13 +10601,13 @@
         <v>80</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>80</v>
@@ -10677,7 +10625,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10686,7 +10634,7 @@
         <v>92</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>161</v>
+        <v>80</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>104</v>
@@ -10695,16 +10643,16 @@
         <v>80</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="AP71" t="s" s="2">
         <v>80</v>
@@ -10712,10 +10660,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10738,19 +10686,19 @@
         <v>80</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>80</v>
@@ -10775,13 +10723,13 @@
         <v>80</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>80</v>
@@ -10799,7 +10747,7 @@
         <v>80</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -10808,7 +10756,7 @@
         <v>92</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>161</v>
+        <v>80</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>104</v>
@@ -10817,27 +10765,27 @@
         <v>80</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>517</v>
+        <v>510</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10860,19 +10808,19 @@
         <v>80</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>522</v>
+        <v>515</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>80</v>
@@ -10897,13 +10845,13 @@
         <v>80</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>80</v>
@@ -10921,7 +10869,7 @@
         <v>80</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -10930,7 +10878,7 @@
         <v>82</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>161</v>
+        <v>80</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>104</v>
@@ -10939,13 +10887,13 @@
         <v>80</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>80</v>
@@ -10956,10 +10904,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10982,19 +10930,19 @@
         <v>93</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>80</v>
@@ -11043,7 +10991,7 @@
         <v>80</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11052,7 +11000,7 @@
         <v>92</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>104</v>
@@ -11061,16 +11009,16 @@
         <v>80</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>80</v>
@@ -11078,10 +11026,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11104,19 +11052,17 @@
         <v>80</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>200</v>
-      </c>
+        <v>531</v>
+      </c>
+      <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>80</v>
@@ -11165,7 +11111,7 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11183,13 +11129,13 @@
         <v>80</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>539</v>
+        <v>532</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>80</v>
@@ -11200,10 +11146,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11226,19 +11172,19 @@
         <v>93</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>543</v>
+        <v>536</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>545</v>
+        <v>538</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>80</v>
@@ -11287,7 +11233,7 @@
         <v>80</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11296,7 +11242,7 @@
         <v>92</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>104</v>
@@ -11305,13 +11251,13 @@
         <v>80</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>547</v>
+        <v>540</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>80</v>
@@ -11322,10 +11268,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>549</v>
+        <v>542</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>549</v>
+        <v>542</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11348,17 +11294,17 @@
         <v>80</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>550</v>
+        <v>543</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>551</v>
+        <v>544</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
-        <v>552</v>
+        <v>545</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>80</v>
@@ -11407,7 +11353,7 @@
         <v>80</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>549</v>
+        <v>542</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11416,7 +11362,7 @@
         <v>82</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>161</v>
+        <v>80</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>104</v>
@@ -11425,13 +11371,13 @@
         <v>80</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>553</v>
+        <v>546</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>80</v>
@@ -11442,10 +11388,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>555</v>
+        <v>548</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>555</v>
+        <v>548</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11468,13 +11414,13 @@
         <v>80</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11525,7 +11471,7 @@
         <v>80</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11543,7 +11489,7 @@
         <v>80</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>80</v>
@@ -11560,10 +11506,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>556</v>
+        <v>549</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>556</v>
+        <v>549</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11592,7 +11538,7 @@
         <v>139</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="N79" t="s" s="2">
         <v>141</v>
@@ -11633,19 +11579,19 @@
         <v>80</v>
       </c>
       <c r="AB79" t="s" s="2">
-        <v>142</v>
+        <v>80</v>
       </c>
       <c r="AC79" t="s" s="2">
-        <v>143</v>
+        <v>80</v>
       </c>
       <c r="AD79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>144</v>
+        <v>80</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -11657,13 +11603,13 @@
         <v>80</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>80</v>
@@ -11680,14 +11626,14 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>557</v>
+        <v>550</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>557</v>
+        <v>550</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -11709,16 +11655,16 @@
         <v>138</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="N80" t="s" s="2">
         <v>141</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>80</v>
@@ -11767,7 +11713,7 @@
         <v>80</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -11779,7 +11725,7 @@
         <v>80</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>80</v>
@@ -11802,10 +11748,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>558</v>
+        <v>551</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>558</v>
+        <v>551</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11828,17 +11774,15 @@
         <v>80</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>559</v>
+        <v>552</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>200</v>
-      </c>
+        <v>553</v>
+      </c>
+      <c r="N81" s="2"/>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>80</v>
@@ -11887,7 +11831,7 @@
         <v>80</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>558</v>
+        <v>551</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>92</v>
@@ -11905,13 +11849,13 @@
         <v>80</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>561</v>
+        <v>554</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>80</v>
@@ -11922,10 +11866,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11948,19 +11892,19 @@
         <v>80</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>565</v>
+        <v>558</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>566</v>
+        <v>559</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>80</v>
@@ -12009,7 +11953,7 @@
         <v>80</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>92</v>
@@ -12018,7 +11962,7 @@
         <v>92</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>161</v>
+        <v>80</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>104</v>
@@ -12027,13 +11971,13 @@
         <v>80</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>569</v>
+        <v>562</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>80</v>
